--- a/docs/tseadfwd/977/OPEN_QUESTIONS_977.xlsx
+++ b/docs/tseadfwd/977/OPEN_QUESTIONS_977.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Questions'!$A$1:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Questions'!$A$1:$K$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Questions'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -71,22 +71,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008A6D1F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDECEA"/>
+        <fgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF6D8"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -145,40 +135,34 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -585,7 +569,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Open 16</t>
+          <t>Answered 12, Resolved 4</t>
         </is>
       </c>
     </row>
@@ -696,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -710,7 +694,6 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -769,938 +752,921 @@
           <t>Related</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
-        <is>
-          <t>BUSINESS ANSWER</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="88.2" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    </row>
+    <row r="2" ht="100.8" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Scope / Inputs</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Which two files does the report compare?</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>The US says 'the 2 selected files'. The manual Risk workbook (Compare_RA_BCEF_KO_Prod 26Q2.xlsx) compares two INPUTS_RA workbooks: the file the team is about to use (Updated) against the one used at the previous reference (Previous). The same wording is also readable as two ENGINE OUTPUTS (two TS_EAD_FWD term structures), which would be a different report - and that side is already covered by the existing EadFwdCompare job. Only INPUTS_RA carries FWL_TYPE, the four metrics and the 361 monthly columns the report needs, which is why the default is INPUTS_RA.</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Reference model compares two INPUTS_RA workbooks (Inputs_RA_v2 against Inputs_RA).</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Confirm the two selected files are INPUTS_RA workbooks, not two TS_EAD_FWD outputs.</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Default chosen so the build can start: two INPUTS_RA workbooks.</t>
-        </is>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): two INPUTS_RA workbooks, named in a new configuration block. Block spelled COMPARE_AND_REPORT to match every other block in application.conf (the answer wrote compare_and_report; HOCON is case-sensitive and the file is UPPER_SNAKE throughout).</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>design 10.Q1</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr"/>
     </row>
     <row r="3" ht="50.4" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Layout</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Is the first month column called M0 or M1?</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>The INPUTS_RA sheets label the first monthly column M1. The manual Risk report labels the same column M0. The US text says 'all months (M1 to M361)'. Same month, three namings - it only affects the label shown on the month index row and on the chart x-axis, never a value.</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Reference model keeps the input's own M1..M361 labels.</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>Confirm the label the business wants to read: M1..M361 (as in the input and the US) or M0..M360 (as in the manual file).</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>Default: keep the input's M1..M361.</t>
-        </is>
-      </c>
-      <c r="I3" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): M1..M361, as in the INPUTS_RA file. The manual file's M0 is not reproduced.</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>design 10.Q2</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr"/>
     </row>
     <row r="4" ht="75.59999999999999" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Alignment</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>How are the two files aligned when their as-of dates differ?</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>In the manual workbook Updated starts 01/04/2026 and Previous starts 01/01/2026 - a quarter apart - and the Evol formula still reads =(C5-C42)/C42, column C against column C. So the two files are aligned by MONTH INDEX and the dates are labels, not join keys: M1-of-new is compared with M1-of-old even though they are different calendar months. The alternative, aligning by calendar month and comparing only the overlapping dates, is a materially different report and would drop the first quarter of one file.</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Reference model aligns by month INDEX; dates are display labels only.</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Confirm alignment by month index (like-for-like projection month) rather than by calendar date.</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Default: by month index, reproducing the manual file.</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): alignment by month INDEX. Dates are dropped from the report entirely, so the question of differing as-of dates no longer arises: months are identified as M1..M361 everywhere.</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Q4; design 10.Q3</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr"/>
-    </row>
-    <row r="5" ht="50.4" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+    </row>
+    <row r="5" ht="75.59999999999999" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Inputs</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Where do the column dates come from?</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>An INPUTS_RA sheet carries no as-of date anywhere - only M1..M361. The dates printed on each table header in the manual file must therefore be supplied from outside the file. In the reference model they were passed on the command line (--new-start 2026-01, --old-start 2025-10).</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Reference model takes one start month per side from configuration (newStart / oldStart).</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Confirm the first projection month of each side is a configuration parameter, or tell us where the as-of date of an INPUTS_RA file should be read from.</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>Default: config parameter per side. Alternative: reuse parameters.as_of_date_quarter for the new file and require the old one explicitly.</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): no dates anywhere in the report - the table header rows carry M1..M361 instead of calendar months. newStart / oldStart are therefore NOT needed in the configuration.</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Q3; design 10.Q4</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr"/>
-    </row>
-    <row r="6" ht="50.4" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    </row>
+    <row r="6" ht="88.2" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Computation</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>What should a cell show when the previous value is zero?</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>The %change formula (new - old) / old is undefined when old = 0. The manual workbook leaves the Excel error #DIV/0! visible in those cells. The engine can reproduce that or blank the cell and list the case. This is not hypothetical: it happens today on CONSO, whose RA FI and RE rows are zero on both sides.</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Reference model wraps every formula in IFERROR so the cell is blank; a --raw-div switch reproduces the bare #DIV/0!.</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Confirm: blank cell plus a 'not computable' list in the report (proposed), or keep #DIV/0! visible as the manual file does.</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Proposed defaults: old 0 and new 0 -&gt; blank; old 0 and new non-zero -&gt; blank plus listed; old present and new missing -&gt; blank plus listed.</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): the proposed defaults are accepted: old 0 and new 0 -&gt; blank; old 0 and new non-zero -&gt; blank plus listed; old present and new missing -&gt; blank plus listed. The manual file's visible #DIV/0! is not reproduced.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>design 10.Q5</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr"/>
     </row>
     <row r="7" ht="138.6" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Derived rows</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Where does the %RA row (row 10) come from, and is the x12 annualisation right?</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>%RA is NOT a column of INPUTS_RA and is NOT mentioned anywhere in the US wording. It is a DERIVED row, reverse-engineered from the manual Risk workbook where it sits as the 6th row of every segment table. In the reference model it is a live Excel formula on row 10: =IFERROR(C6*12/-C5) - where C6 is the RA row (row 6, itself =C7+C8+C9, that is RA STAT + RA FI + RE) and C5 is CRD, which is negative in the input. The full chain is therefore %RA = (RA STAT + RA FI + RE) x 12 / -CRD, an annualised loss rate over the outstanding. The x12 was INFERRED, not specified: it reads the RA metrics as MONTHLY flows and CRD as the outstanding of that same month, so multiplying by 12 turns a monthly rate into an annual one. Cross-check against the manual file (Immos, first month): RA STAT 373 + RA FI 10 + RE 6 = 389, and 389 x 12 / 93 172 = 5.01 percent against the 5.02 percent the file displays - close enough to confirm the shape of the formula, but NOT an exact reproduction (see Q13).</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Reference model row 10 = IFERROR(RA x 12 / -CRD), with RA on row 6 = RA STAT + RA FI + RE. Stated on the COMPARE INFO sheet as '%RA = RA x 12 / -CRD (annualised rate over the outstanding)'.</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>(1) Confirm %RA = (RA STAT + RA FI + RE) x 12 / -CRD. (2) Confirm the annualisation factor is 12 for every table, and would not change if the report were ever produced on a quarterly or yearly grid. (3) Confirm the -CRD sign convention (CRD is negative in the input) so %RA reads as a positive percentage.</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>Reverse-engineered from the manual workbook and matching its displayed percentage to the second decimal; pending business confirmation.</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): %RA is DROPPED. The report carries only the four metrics present in the INPUTS_RA file (CRD, RA STAT, RA FI, RE); no derived row is computed, so the x12 annualisation and its denominator no longer arise. Confirmed for the RA subtotal too - see Q11.</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>Q11, Q12, Q13; design 10.Q6</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr"/>
     </row>
     <row r="8" ht="75.59999999999999" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Q7</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Acceptance</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Can we have the manual workbook and the two inputs it was built from?</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>The US acceptance criterion is 'test the generated reports against the manual calculations'. To do that as a numeric diff rather than a reading exercise we need the manual file Compare_RA_BCEF_KO_Prod 26Q2.xlsx AND the two INPUTS_RA workbooks it was produced from. Without them the reconciliation can only run on the pair available in the repo, which are the same vintage at two different roundings - so their Evol block is rounding noise (about 1e-5) and proves nothing about the business logic.</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Reference model was built from Inputs_RA_v2 against Inputs_RA, whose differences are rounding only.</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Provide Compare_RA_BCEF_KO_Prod 26Q2.xlsx and the two INPUTS_RA files used to build it, so the generated report can be reconciled cell by cell.</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): not needed for now; reconciliation against the manual workbook will be done later. Acceptance test T6 is therefore deferred, and T1-T5/T7 stand.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>design 10.Q7</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr"/>
     </row>
     <row r="9" ht="50.4" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Excel, HTML, or both from TWIST?</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>The US says the report should be 'a new excel/HTML report output available from TWIST in a new tab on EAD FWL TS tool' without deciding which. The two are different deliverables: the workbook carries live formulas a reviewer can click and audit, the HTML page is a read-only in-browser preview.</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Reference model produces the Excel workbook. The HTML page is designed but not built.</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Confirm what the new TWIST tab must serve: the Excel workbook, an HTML page, or both.</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>Default: Excel is the deliverable, HTML is the in-browser preview.</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): Excel is the deliverable. HTML is not built for now and will be revisited if TWIST needs it.</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>design 10.Q8</t>
         </is>
       </c>
-      <c r="L9" s="11" t="inlineStr"/>
     </row>
     <row r="10" ht="50.4" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>One workbook for every perimeter, or one file per perimeter?</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>The manual file covers one perimeter (BCEF) because it is written by hand. The engine can produce every perimeter in one run. With 6 perimeters and 3 stress legs that is 18 sheets and roughly 288 charts in a single workbook - large but workable - against 6 smaller files.</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Reference model writes one workbook: three sheets per perimeter (BASELINE, -100, +100) plus COMPARE INFO.</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Confirm one workbook containing every perimeter, or one file per perimeter if that is what TWIST serves.</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Default: one workbook.</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): one workbook for every perimeter.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>Q15; design 10.Q9</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="37.8" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Should a material %change be highlighted?</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Nothing in the US asks for it. A conditional format above a configurable threshold (for example an absolute %change above 5 percent) would turn the Evol block from a wall of numbers into something a reviewer can scan for the months that actually moved.</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Reference model applies no highlighting.</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Confirm whether the Evol block should highlight changes above a threshold, and if so what the threshold is.</t>
         </is>
       </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>Off by default.</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): no highlighting.</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>design 10.Q10</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    </row>
+    <row r="12" ht="113.4" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Derived rows</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Is RA = RA STAT + RA FI + RE, and why is the Evol row labelled RA/RE?</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Like %RA, the RA row is derived: it appears in neither the INPUTS_RA file nor the US wording. In the Updated and Previous blocks it is row 6 = RA STAT + RA FI + RE. In the Evol block the same row is labelled 'RA/RE' (row 80) while its formula =(C6-C43)/C43 is the %change of the RA row - so the label and the content disagree. The label was carried over from the manual workbook rather than silently corrected.</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Reference model computes RA = RA STAT + RA FI + RE in all three blocks; the Evol row keeps the manual file's 'RA/RE' label.</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>(1) Confirm RA = RA STAT + RA FI + RE. (2) Tell us whether the Evol row should read 'RA', matching what it computes, or stay 'RA/RE' to match the manual report the team is used to.</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Definition taken from the manual workbook; the label mismatch is reproduced deliberately and flagged here.</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): both derived rows are dropped. The answer named only %RA, and Q6 said to work only from the four input metrics; confirmed on 2026-08-27 that the RA subtotal goes too. A segment table is therefore four rows - CRD, RA STAT, RA FI, RE - and the RA/RE label question disappears with the row.</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="88.2" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Derived rows</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>In the Evol block, should %RA be a relative change or a difference in percentage points?</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Every Evol cell applies the same formula (new - old) / old. On the four metric rows that is a relative change and is clearly right. On row 84 the same formula is applied to %RA, which is ALREADY a rate: =(C10-C47)/C47 gives the relative change of a percentage. Business reporting usually expresses the move of a rate in PERCENTAGE POINTS (new - old) instead. Example: 5.00 percent against 4.00 percent reads as +25 percent under the current formula, or as +1.00 point under the other convention - the same fact, two very different numbers on the page.</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Reference model applies (new - old) / old to the %RA row too, reproducing the manual workbook.</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Confirm whether the %RA line of the Evol block should stay a relative change, or become a percentage-point difference.</t>
         </is>
       </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>Current behaviour reproduces the manual file; flagged because the formula is being applied to a rate rather than to an amount.</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): moot: %RA is dropped, so no Evol cell is ever applied to a rate. Every Evol cell is now (new - old) / old over an amount, which is the unambiguous case.</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K13" s="13" t="inlineStr">
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="L13" s="11" t="inlineStr"/>
     </row>
     <row r="14" ht="75.59999999999999" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Derived rows</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Which CRD does the %RA denominator use?</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Recomputing the manual file's own numbers gives 5.01 percent where the file displays 5.02 percent (Immos, first month). The gap is small but systematic enough to ask about: it is explained either by the manual file simply rounding for display, or by its denominator not being the same-month CRD - for instance an average of the opening and closing outstanding, or the previous month's CRD. The two readings diverge visibly once the outstanding is running off quickly.</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Reference model divides by the CRD of the SAME month (-C5 on row 10).</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Confirm the denominator is the outstanding of the same month, and not an average or a previous-month CRD.</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Same-month CRD assumed; the residual 5.01 against 5.02 is believed to be display rounding but has not been confirmed.</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): moot: the denominator only mattered for %RA, which is dropped. (The answer given, same-month CRD, is recorded should %RA ever be reinstated.)</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15" ht="63" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+    </row>
+    <row r="15" ht="75.59999999999999" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Layout</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Are the French segment labels canonical, and what is used for a new segment?</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>The report does not print the technical segment names. It prints 'Immos a TF', 'Invest pro a TF', 'Invest corp a TF', 'Conso a TF' - a display label joined to RATE_TYPE - taken from the manual workbook, in that fixed order. A segment that is not one of those four has no label and no defined position.</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Reference model maps MORTGAGE to Immos, INVEST_PRO to Invest pro, INVEST_CORP to Invest corp, CONSO to Conso, in that order, then anything else alphabetically under its raw technical name.</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Confirm the four labels and their order, and tell us what label a new segment should carry, or whether the raw technical name is acceptable.</t>
         </is>
       </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>Labels and order reproduced from the manual workbook.</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): use the segment names as they appear in the INPUTS_RA file (MORTGAGE, INVEST_PRO, INVEST_CORP, CONSO), NOT the manual file's French labels. The display ORDER is a configuration parameter.</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="L15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="63" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Which perimeters and rate types are in scope for this report?</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>The manual file covers BCEF only. The current input workbook carries six perimeters (BCEF, BGL, BNL, FORTIS, LS, OLA) and today only rate type TF. The report compares the intersection of the two files on the full key, so anything present in only one file is excluded and named in the report rather than silently dropped - comparing Inputs_RA_v4 (6 perimeters) against Inputs_RA (BCEF only) compares 48 keys and drops 240.</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Reference model compares every perimeter common to both files; the configured perimeter list is empty, meaning all.</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Confirm the report should cover every common perimeter, or name the perimeters and rate types that belong in it.</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Default: every perimeter common to both files.</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): every perimeter common to both files.</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>Q9, Q14</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="50.4" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+    </row>
+    <row r="17" ht="88.2" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Inputs</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Are the input values always in millions of euros?</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Each block of the report is headed 'En M EUR' and no rescaling is applied anywhere - the report shows the input exactly as it is, as the manual file does. That header is therefore an assertion about the input rather than a conversion. If an INPUTS_RA file ever arrived in units, every printed figure and the header would both be wrong, silently.</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Reference model prints values unchanged and labels the block 'En M EUR'.</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>Confirm INPUTS_RA values are always delivered in millions of euros, and that CRD is always negative (exposure).</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>Assumed from the manual workbook and from the current input files.</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>DECISION (business 2026-08-27): values are used exactly as they appear in the INPUTS_RA file, with no rescaling - the same convention the RA calculation already uses. The manual file's 'En M EUR' block header is an assertion about the input, not a conversion.</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K17" s="13" t="inlineStr">
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="L17" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L17"/>
+  <autoFilter ref="A1:K17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>